--- a/Donnees/Statistiques Economiques/Transport et Communication_2.xlsx
+++ b/Donnees/Statistiques Economiques/Transport et Communication_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Economiques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DA8606-DDB8-432A-B778-34B6006AE66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569C9CFF-93BE-44D7-BFC0-C6A63C5E16DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB999371-695F-4B71-807B-4E369D1A42C3}"/>
   </bookViews>
@@ -27,25 +27,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Passagers~Arrivé (nombre)</t>
+    <t xml:space="preserve">Passagers~Départ </t>
   </si>
   <si>
-    <t>Passagers~Total            (nombre)</t>
+    <t>Passagers~Total</t>
   </si>
   <si>
-    <t>Passagers~Départ (nombre)</t>
+    <t xml:space="preserve">Mouvements d'avions~Départ </t>
   </si>
   <si>
-    <t>Mouvements d'avions~Arrivé (nombre)</t>
+    <t>Tableau 4.11.4 : Évolution mensuelle du trafic aérien (nombre)</t>
   </si>
   <si>
-    <t>Mouvements d'avions~Départ (nombre)</t>
+    <t>Source: ANAC</t>
   </si>
   <si>
-    <t>Source: Agence Nationale de l'Aviation Civile</t>
+    <t xml:space="preserve">Passagers~Arrivée </t>
   </si>
   <si>
-    <t>Tableau: Evolution mensuelle du trafic aerien</t>
+    <t xml:space="preserve">Mouvements d'avions~Arrivée </t>
   </si>
 </sst>
 </file>
@@ -568,10 +568,11 @@
   <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="48.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.109375" customWidth="1"/>
     <col min="9" max="9" width="18.88671875" customWidth="1"/>
   </cols>
@@ -579,25 +580,25 @@
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.6" x14ac:dyDescent="0.7">
@@ -3716,7 +3717,7 @@
     </row>
     <row r="160" spans="1:6" ht="24.6" x14ac:dyDescent="0.7">
       <c r="A160" s="17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
